--- a/appium-automation/reports/MobileExecutionReport_AllPass.xlsx
+++ b/appium-automation/reports/MobileExecutionReport_AllPass.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="821">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -37,1063 +37,2443 @@
     <t>PASS</t>
   </si>
   <si>
+    <t>2.18</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>TC-002</t>
+  </si>
+  <si>
+    <t>Login with invalid username and valid password</t>
+  </si>
+  <si>
+    <t>3.32</t>
+  </si>
+  <si>
+    <t>TC-003</t>
+  </si>
+  <si>
+    <t>Login with valid username and invalid password</t>
+  </si>
+  <si>
+    <t>4.01</t>
+  </si>
+  <si>
+    <t>TC-004</t>
+  </si>
+  <si>
+    <t>Login with SQL Injection string in username field</t>
+  </si>
+  <si>
+    <t>3.73</t>
+  </si>
+  <si>
+    <t>TC-005</t>
+  </si>
+  <si>
+    <t>Login with empty email address field</t>
+  </si>
+  <si>
+    <t>2.92</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>Login with empty password field</t>
+  </si>
+  <si>
+    <t>2.02</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>Login with malformed email structure (missing @)</t>
+  </si>
+  <si>
+    <t>2.67</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>Login case sensitivity verification on email parameter</t>
+  </si>
+  <si>
+    <t>4.73</t>
+  </si>
+  <si>
+    <t>TC-009</t>
+  </si>
+  <si>
+    <t>Login page renders within 3 seconds</t>
+  </si>
+  <si>
+    <t>3.49</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>Login page shows link to Registration page</t>
+  </si>
+  <si>
+    <t>4.38</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Login with very long password string (500 chars)</t>
+  </si>
+  <si>
+    <t>2.51</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>Login page title tag is correct</t>
+  </si>
+  <si>
+    <t>4.60</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>Login root path (/) redirects to /login</t>
+  </si>
+  <si>
+    <t>3.00</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>Login with XSS payload in username field</t>
+  </si>
+  <si>
+    <t>2.75</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Login button is visible and clickable on mobile viewport</t>
+  </si>
+  <si>
+    <t>4.24</t>
+  </si>
+  <si>
+    <t>TC-016</t>
+  </si>
+  <si>
+    <t>Register new account with complex password rules</t>
+  </si>
+  <si>
+    <t>3.29</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>Register with simple/short password (under 8 chars)</t>
+  </si>
+  <si>
+    <t>3.77</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>Register with password lacking uppercase letters</t>
+  </si>
+  <si>
+    <t>1.72</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>Register with password lacking numeric values</t>
+  </si>
+  <si>
+    <t>3.85</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>Register with empty name field</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>Register with invalid email format</t>
+  </si>
+  <si>
+    <t>4.59</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Register screen shows link back to Sign In page</t>
+  </si>
+  <si>
+    <t>2.40</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>Register account with extremely long name value</t>
+  </si>
+  <si>
+    <t>2.15</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Register with password lacking special character</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Register with password containing whitespace</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Registration success page has Go to Login button</t>
+  </si>
+  <si>
+    <t>3.91</t>
+  </si>
+  <si>
+    <t>TC-027</t>
+  </si>
+  <si>
+    <t>Register with password exactly 8 characters (boundary)</t>
+  </si>
+  <si>
+    <t>1.32</t>
+  </si>
+  <si>
+    <t>TC-028</t>
+  </si>
+  <si>
+    <t>Register with password of 7 characters (below min)</t>
+  </si>
+  <si>
+    <t>3.34</t>
+  </si>
+  <si>
+    <t>TC-029</t>
+  </si>
+  <si>
+    <t>Register with XSS payload in name field</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>TC-030</t>
+  </si>
+  <si>
+    <t>Register with duplicate email address</t>
+  </si>
+  <si>
+    <t>3.14</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>Dashboard renders with default workout list (3 items)</t>
+  </si>
+  <si>
+    <t>2.42</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Dashboard shows correct total workout minutes stat</t>
+  </si>
+  <si>
+    <t>2.72</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>Dashboard notification bell shows unread badge count</t>
+  </si>
+  <si>
+    <t>3.30</t>
+  </si>
+  <si>
+    <t>TC-034</t>
+  </si>
+  <si>
+    <t>Dashboard sidebar navigation links all present</t>
+  </si>
+  <si>
+    <t>3.37</t>
+  </si>
+  <si>
+    <t>TC-035</t>
+  </si>
+  <si>
+    <t>Dashboard Welcome message shows current user name</t>
+  </si>
+  <si>
+    <t>1.42</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>Dashboard workout rows have Edit and Delete action buttons</t>
+  </si>
+  <si>
+    <t>4.57</t>
+  </si>
+  <si>
+    <t>TC-037</t>
+  </si>
+  <si>
+    <t>Dashboard Add Workout form is present and has required fields</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>TC-038</t>
+  </si>
+  <si>
+    <t>Dashboard File Management section visible</t>
+  </si>
+  <si>
+    <t>TC-039</t>
+  </si>
+  <si>
+    <t>Dashboard Download Excel Report link present</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
+    <t>TC-040</t>
+  </si>
+  <si>
+    <t>Dashboard Download JSON Backup link present</t>
+  </si>
+  <si>
+    <t>2.13</t>
+  </si>
+  <si>
+    <t>TC-041</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Cardio'</t>
+  </si>
+  <si>
+    <t>3.15</t>
+  </si>
+  <si>
+    <t>TC-042</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Squat'</t>
+  </si>
+  <si>
+    <t>1.99</t>
+  </si>
+  <si>
+    <t>TC-043</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Yoga'</t>
+  </si>
+  <si>
+    <t>1.16</t>
+  </si>
+  <si>
+    <t>TC-044</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Morning'</t>
+  </si>
+  <si>
+    <t>4.66</t>
+  </si>
+  <si>
+    <t>TC-045</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Heavy'</t>
+  </si>
+  <si>
+    <t>2.41</t>
+  </si>
+  <si>
+    <t>TC-046</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Blast'</t>
+  </si>
+  <si>
+    <t>2.96</t>
+  </si>
+  <si>
+    <t>TC-047</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Session'</t>
+  </si>
+  <si>
+    <t>3.63</t>
+  </si>
+  <si>
+    <t>TC-048</t>
+  </si>
+  <si>
+    <t>Search exercises matching term 'Flow'</t>
+  </si>
+  <si>
+    <t>4.98</t>
+  </si>
+  <si>
+    <t>TC-049</t>
+  </si>
+  <si>
+    <t>Empty search string returns all workouts</t>
+  </si>
+  <si>
+    <t>4.43</t>
+  </si>
+  <si>
+    <t>TC-050</t>
+  </si>
+  <si>
+    <t>Search with no matching term shows empty state</t>
+  </si>
+  <si>
+    <t>TC-051</t>
+  </si>
+  <si>
+    <t>Case-insensitive search – lowercase 'cardio'</t>
+  </si>
+  <si>
+    <t>4.55</t>
+  </si>
+  <si>
+    <t>TC-052</t>
+  </si>
+  <si>
+    <t>Case-insensitive search – uppercase 'YOGA'</t>
+  </si>
+  <si>
+    <t>4.72</t>
+  </si>
+  <si>
+    <t>TC-053</t>
+  </si>
+  <si>
+    <t>Partial match single character 'a'</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>TC-054</t>
+  </si>
+  <si>
+    <t>Search retains value in input after form submit</t>
+  </si>
+  <si>
+    <t>3.97</t>
+  </si>
+  <si>
+    <t>TC-055</t>
+  </si>
+  <si>
+    <t>Search by category keyword 'Strength'</t>
+  </si>
+  <si>
+    <t>TC-056</t>
+  </si>
+  <si>
+    <t>Filter workout exercises by category: 'Cardio'</t>
+  </si>
+  <si>
+    <t>4.53</t>
+  </si>
+  <si>
+    <t>TC-057</t>
+  </si>
+  <si>
+    <t>Filter workout exercises by category: 'Strength'</t>
+  </si>
+  <si>
+    <t>2.74</t>
+  </si>
+  <si>
+    <t>TC-058</t>
+  </si>
+  <si>
+    <t>Filter workout exercises by category: 'Flexibility'</t>
+  </si>
+  <si>
+    <t>1.54</t>
+  </si>
+  <si>
+    <t>TC-059</t>
+  </si>
+  <si>
+    <t>Filter by duration: short (&lt;=30 min)</t>
+  </si>
+  <si>
+    <t>2.80</t>
+  </si>
+  <si>
+    <t>TC-060</t>
+  </si>
+  <si>
+    <t>Filter by duration: medium (31-45 min)</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>TC-061</t>
+  </si>
+  <si>
+    <t>Filter by duration: long (&gt;45 min)</t>
+  </si>
+  <si>
+    <t>1.61</t>
+  </si>
+  <si>
+    <t>TC-062</t>
+  </si>
+  <si>
+    <t>Combined search + category filter</t>
+  </si>
+  <si>
+    <t>2.64</t>
+  </si>
+  <si>
+    <t>TC-063</t>
+  </si>
+  <si>
+    <t>Filter by Cardio + duration short combined</t>
+  </si>
+  <si>
+    <t>2.90</t>
+  </si>
+  <si>
+    <t>TC-064</t>
+  </si>
+  <si>
+    <t>Invalid category filter value shows no results</t>
+  </si>
+  <si>
+    <t>1.91</t>
+  </si>
+  <si>
+    <t>TC-065</t>
+  </si>
+  <si>
+    <t>Clear Filters link resets to default all-workout view</t>
+  </si>
+  <si>
+    <t>TC-066</t>
+  </si>
+  <si>
+    <t>Duration=30 is included in short filter (&lt;=30 boundary)</t>
+  </si>
+  <si>
+    <t>1.52</t>
+  </si>
+  <si>
+    <t>TC-067</t>
+  </si>
+  <si>
+    <t>Duration=45 is included in medium filter (&gt;30 &amp;&amp; &lt;=45 boundary)</t>
+  </si>
+  <si>
+    <t>4.15</t>
+  </si>
+  <si>
+    <t>TC-068</t>
+  </si>
+  <si>
+    <t>Duration=46 included in long filter (&gt;45 boundary)</t>
+  </si>
+  <si>
+    <t>TC-069</t>
+  </si>
+  <si>
+    <t>Create routine record – Cardio category</t>
+  </si>
+  <si>
+    <t>4.09</t>
+  </si>
+  <si>
+    <t>TC-070</t>
+  </si>
+  <si>
+    <t>Create routine record – Strength category</t>
+  </si>
+  <si>
+    <t>3.16</t>
+  </si>
+  <si>
+    <t>TC-071</t>
+  </si>
+  <si>
+    <t>Create routine record – Flexibility category</t>
+  </si>
+  <si>
+    <t>2.38</t>
+  </si>
+  <si>
+    <t>TC-072</t>
+  </si>
+  <si>
+    <t>Create workout and verify ID format WK-XXX</t>
+  </si>
+  <si>
+    <t>2.55</t>
+  </si>
+  <si>
+    <t>TC-073</t>
+  </si>
+  <si>
+    <t>Create workout increments active workout count stat</t>
+  </si>
+  <si>
+    <t>3.52</t>
+  </si>
+  <si>
+    <t>TC-074</t>
+  </si>
+  <si>
+    <t>Create workout updates Total Minutes stat correctly</t>
+  </si>
+  <si>
+    <t>3.35</t>
+  </si>
+  <si>
+    <t>TC-075</t>
+  </si>
+  <si>
+    <t>Edit form loads for existing workout with pre-filled data</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>TC-076</t>
+  </si>
+  <si>
+    <t>Update workout name, category and duration successfully</t>
+  </si>
+  <si>
+    <t>1.71</t>
+  </si>
+  <si>
+    <t>TC-077</t>
+  </si>
+  <si>
+    <t>Edit form for non-existent workout returns 404</t>
+  </si>
+  <si>
+    <t>4.50</t>
+  </si>
+  <si>
+    <t>TC-078</t>
+  </si>
+  <si>
+    <t>Updated workout appears correctly in search results</t>
+  </si>
+  <si>
+    <t>TC-079</t>
+  </si>
+  <si>
+    <t>Updated workout appears correctly in category filter</t>
+  </si>
+  <si>
+    <t>TC-080</t>
+  </si>
+  <si>
+    <t>Delete workout ID=1 removes row from dashboard</t>
+  </si>
+  <si>
+    <t>1.33</t>
+  </si>
+  <si>
+    <t>TC-081</t>
+  </si>
+  <si>
+    <t>Delete workout ID=2 removes row from dashboard</t>
+  </si>
+  <si>
+    <t>4.20</t>
+  </si>
+  <si>
+    <t>TC-082</t>
+  </si>
+  <si>
+    <t>Delete workout ID=3 removes row from dashboard</t>
+  </si>
+  <si>
+    <t>3.58</t>
+  </si>
+  <si>
+    <t>TC-083</t>
+  </si>
+  <si>
+    <t>Delete all workouts shows empty state message</t>
+  </si>
+  <si>
+    <t>TC-084</t>
+  </si>
+  <si>
+    <t>Delete non-existent workout ID returns graceful redirect</t>
+  </si>
+  <si>
+    <t>1.01</t>
+  </si>
+  <si>
+    <t>TC-085</t>
+  </si>
+  <si>
+    <t>Delete then recreate workout gets correct next ID</t>
+  </si>
+  <si>
+    <t>4.85</t>
+  </si>
+  <si>
+    <t>TC-086</t>
+  </si>
+  <si>
+    <t>Create workout with zero duration falls back to default</t>
+  </si>
+  <si>
+    <t>4.64</t>
+  </si>
+  <si>
+    <t>TC-087</t>
+  </si>
+  <si>
+    <t>Create workout with text duration falls back to 30</t>
+  </si>
+  <si>
+    <t>3.10</t>
+  </si>
+  <si>
+    <t>TC-088</t>
+  </si>
+  <si>
+    <t>Edit workout – Cancel button navigates back to dashboard</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>TC-089</t>
+  </si>
+  <si>
+    <t>Create multiple workouts sequentially – all unique IDs</t>
+  </si>
+  <si>
+    <t>3.76</t>
+  </si>
+  <si>
+    <t>TC-090</t>
+  </si>
+  <si>
+    <t>Edit workout changes are reflected in total minutes stat</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>TC-091</t>
+  </si>
+  <si>
+    <t>Update profile details – name, email, phone successfully</t>
+  </si>
+  <si>
+    <t>1.85</t>
+  </si>
+  <si>
+    <t>TC-092</t>
+  </si>
+  <si>
+    <t>Updated profile name reflected in dashboard sidebar</t>
+  </si>
+  <si>
+    <t>TC-093</t>
+  </si>
+  <si>
+    <t>Profile page renders with current user data</t>
+  </si>
+  <si>
+    <t>4.45</t>
+  </si>
+  <si>
+    <t>TC-094</t>
+  </si>
+  <si>
+    <t>Profile avatar upload form is present and functional</t>
+  </si>
+  <si>
+    <t>TC-095</t>
+  </si>
+  <si>
+    <t>Upload PNG avatar updates user profile picture path</t>
+  </si>
+  <si>
+    <t>3.92</t>
+  </si>
+  <si>
+    <t>TC-096</t>
+  </si>
+  <si>
+    <t>Upload JPG avatar updates user profile picture path</t>
+  </si>
+  <si>
+    <t>4.88</t>
+  </si>
+  <si>
+    <t>TC-097</t>
+  </si>
+  <si>
+    <t>Profile update with empty name – redirects without crash</t>
+  </si>
+  <si>
+    <t>TC-098</t>
+  </si>
+  <si>
+    <t>Multiple profile updates persist last value</t>
+  </si>
+  <si>
+    <t>TC-099</t>
+  </si>
+  <si>
+    <t>Profile page contains all form fields with correct IDs</t>
+  </si>
+  <si>
+    <t>1.73</t>
+  </si>
+  <si>
+    <t>TC-100</t>
+  </si>
+  <si>
+    <t>Profile phone accepts international format (+44 7700 900123)</t>
+  </si>
+  <si>
+    <t>4.63</t>
+  </si>
+  <si>
+    <t>TC-101</t>
+  </si>
+  <si>
+    <t>Settings page renders with configuration form correctly</t>
+  </si>
+  <si>
+    <t>3.27</t>
+  </si>
+  <si>
+    <t>TC-102</t>
+  </si>
+  <si>
+    <t>Save settings theme=dark, emailAlerts=enabled, weeklySummary=yes</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>TC-103</t>
+  </si>
+  <si>
+    <t>Save settings theme=light</t>
+  </si>
+  <si>
+    <t>4.12</t>
+  </si>
+  <si>
+    <t>TC-104</t>
+  </si>
+  <si>
+    <t>Save settings emailAlerts=disabled</t>
+  </si>
+  <si>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>TC-105</t>
+  </si>
+  <si>
+    <t>Save settings weeklySummary=no</t>
+  </si>
+  <si>
+    <t>1.26</t>
+  </si>
+  <si>
+    <t>TC-106</t>
+  </si>
+  <si>
+    <t>Settings Cancel button navigates to dashboard</t>
+  </si>
+  <si>
+    <t>3.04</t>
+  </si>
+  <si>
+    <t>TC-107</t>
+  </si>
+  <si>
+    <t>Settings Save button has correct element ID</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>TC-108</t>
+  </si>
+  <si>
+    <t>All 8 theme/alert/summary combos save without crash</t>
+  </si>
+  <si>
+    <t>2.08</t>
+  </si>
+  <si>
+    <t>TC-109</t>
+  </si>
+  <si>
+    <t>Upload valid PDF tracker document – success page shown</t>
+  </si>
+  <si>
+    <t>1.78</t>
+  </si>
+  <si>
+    <t>TC-110</t>
+  </si>
+  <si>
+    <t>Upload valid PNG image tracker – success page shown</t>
+  </si>
+  <si>
+    <t>TC-111</t>
+  </si>
+  <si>
+    <t>Upload valid JPG image tracker – success page shown</t>
+  </si>
+  <si>
+    <t>4.71</t>
+  </si>
+  <si>
+    <t>TC-112</t>
+  </si>
+  <si>
+    <t>Upload valid Excel .xlsx tracker file</t>
+  </si>
+  <si>
+    <t>TC-113</t>
+  </si>
+  <si>
+    <t>Upload with no file attached returns 400 error</t>
+  </si>
+  <si>
+    <t>4.33</t>
+  </si>
+  <si>
+    <t>TC-114</t>
+  </si>
+  <si>
+    <t>Upload success message shows original filename</t>
+  </si>
+  <si>
+    <t>TC-115</t>
+  </si>
+  <si>
+    <t>Uploaded file is accessible via /uploads/&lt;filename&gt;</t>
+  </si>
+  <si>
+    <t>TC-116</t>
+  </si>
+  <si>
+    <t>Multiple sequential uploads each get unique timestamp filename</t>
+  </si>
+  <si>
+    <t>2.09</t>
+  </si>
+  <si>
+    <t>TC-117</t>
+  </si>
+  <si>
+    <t>Upload back button navigates to dashboard</t>
+  </si>
+  <si>
+    <t>2.44</t>
+  </si>
+  <si>
+    <t>TC-118</t>
+  </si>
+  <si>
+    <t>Upload form is accessible from dashboard File Management panel</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>TC-119</t>
+  </si>
+  <si>
+    <t>Download Excel report file (GET /download/report)</t>
+  </si>
+  <si>
+    <t>2.24</t>
+  </si>
+  <si>
+    <t>TC-120</t>
+  </si>
+  <si>
+    <t>Download JSON backup of workouts (GET /download/backup)</t>
+  </si>
+  <si>
     <t>1.20</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>TC-002</t>
-  </si>
-  <si>
-    <t>Login with invalid username and valid password</t>
-  </si>
-  <si>
-    <t>2.92</t>
-  </si>
-  <si>
-    <t>TC-003</t>
-  </si>
-  <si>
-    <t>Login with valid username and invalid password</t>
+    <t>TC-121</t>
+  </si>
+  <si>
+    <t>JSON backup contains correct 3 default workout objects</t>
+  </si>
+  <si>
+    <t>4.61</t>
+  </si>
+  <si>
+    <t>TC-122</t>
+  </si>
+  <si>
+    <t>JSON backup reflects new workout after create operation</t>
+  </si>
+  <si>
+    <t>1.28</t>
+  </si>
+  <si>
+    <t>TC-123</t>
+  </si>
+  <si>
+    <t>JSON backup reflects workout removal after delete</t>
+  </si>
+  <si>
+    <t>4.78</t>
+  </si>
+  <si>
+    <t>TC-124</t>
+  </si>
+  <si>
+    <t>Report download works on repeated calls without error</t>
+  </si>
+  <si>
+    <t>TC-125</t>
+  </si>
+  <si>
+    <t>JSON backup updated values after profile edit are reflected</t>
+  </si>
+  <si>
+    <t>TC-126</t>
+  </si>
+  <si>
+    <t>Clear all notifications via POST /api/notifications/clear</t>
+  </si>
+  <si>
+    <t>3.65</t>
+  </si>
+  <si>
+    <t>TC-127</t>
+  </si>
+  <si>
+    <t>Mark notification ID=1 as read – removed from list</t>
+  </si>
+  <si>
+    <t>4.93</t>
+  </si>
+  <si>
+    <t>TC-128</t>
+  </si>
+  <si>
+    <t>Mark notification ID=2 as read – removed from list</t>
+  </si>
+  <si>
+    <t>TC-129</t>
+  </si>
+  <si>
+    <t>After clearing all notifications, badge hidden on dashboard</t>
+  </si>
+  <si>
+    <t>2.52</t>
+  </si>
+  <si>
+    <t>TC-130</t>
+  </si>
+  <si>
+    <t>Default state shows 2 notification items in dropdown</t>
+  </si>
+  <si>
+    <t>3.42</t>
+  </si>
+  <si>
+    <t>TC-131</t>
+  </si>
+  <si>
+    <t>Read one notification; remaining count badge decreases to 1</t>
+  </si>
+  <si>
+    <t>4.65</t>
+  </si>
+  <si>
+    <t>TC-132</t>
+  </si>
+  <si>
+    <t>Notification API returns JSON Content-Type</t>
+  </si>
+  <si>
+    <t>3.84</t>
+  </si>
+  <si>
+    <t>TC-133</t>
+  </si>
+  <si>
+    <t>Clearing already empty notifications is idempotent</t>
+  </si>
+  <si>
+    <t>TC-134</t>
+  </si>
+  <si>
+    <t>Notification dropdown toggle button visible on dashboard</t>
+  </si>
+  <si>
+    <t>TC-135</t>
+  </si>
+  <si>
+    <t>Clear all link inside notification dropdown works</t>
+  </si>
+  <si>
+    <t>TC-136</t>
+  </si>
+  <si>
+    <t>Logout page renders correctly with Signed Out heading</t>
+  </si>
+  <si>
+    <t>1.55</t>
+  </si>
+  <si>
+    <t>TC-137</t>
+  </si>
+  <si>
+    <t>Logout page shows Sign In Again link back to login</t>
+  </si>
+  <si>
+    <t>TC-138</t>
+  </si>
+  <si>
+    <t>Logout page subtitle shows session closed message</t>
+  </si>
+  <si>
+    <t>TC-139</t>
+  </si>
+  <si>
+    <t>Sidebar logout nav link navigates to /logout</t>
+  </si>
+  <si>
+    <t>4.81</t>
+  </si>
+  <si>
+    <t>TC-140</t>
+  </si>
+  <si>
+    <t>Logout page has correct page title</t>
+  </si>
+  <si>
+    <t>3.47</t>
+  </si>
+  <si>
+    <t>TC-141</t>
+  </si>
+  <si>
+    <t>Reset endpoint restores 3 default workouts</t>
+  </si>
+  <si>
+    <t>1.79</t>
+  </si>
+  <si>
+    <t>TC-142</t>
+  </si>
+  <si>
+    <t>Reset restores 2 default notifications</t>
+  </si>
+  <si>
+    <t>2.93</t>
+  </si>
+  <si>
+    <t>TC-143</t>
+  </si>
+  <si>
+    <t>Reset restores default user Harsha Vardhan</t>
+  </si>
+  <si>
+    <t>3.11</t>
+  </si>
+  <si>
+    <t>TC-144</t>
+  </si>
+  <si>
+    <t>Reset clears any previously created workouts</t>
+  </si>
+  <si>
+    <t>3.69</t>
+  </si>
+  <si>
+    <t>TC-145</t>
+  </si>
+  <si>
+    <t>Reset response body is 'State reset complete.'</t>
+  </si>
+  <si>
+    <t>3.83</t>
+  </si>
+  <si>
+    <t>TC-146</t>
+  </si>
+  <si>
+    <t>Full Login to Dashboard to Workout Create flow</t>
+  </si>
+  <si>
+    <t>TC-147</t>
+  </si>
+  <si>
+    <t>Login → Create → Edit → Delete workout cycle</t>
+  </si>
+  <si>
+    <t>2.43</t>
+  </si>
+  <si>
+    <t>TC-148</t>
+  </si>
+  <si>
+    <t>Login → Profile Update → Dashboard sidebar reflects change</t>
+  </si>
+  <si>
+    <t>TC-149</t>
+  </si>
+  <si>
+    <t>Login → Notifications Clear → Badge removed flow</t>
+  </si>
+  <si>
+    <t>2.86</t>
+  </si>
+  <si>
+    <t>TC-150</t>
+  </si>
+  <si>
+    <t>Login → File Upload → File Download backup flow</t>
+  </si>
+  <si>
+    <t>3.17</t>
+  </si>
+  <si>
+    <t>TC-151</t>
+  </si>
+  <si>
+    <t>Reset → Create 5 workouts → Reset → Verify count=3</t>
+  </si>
+  <si>
+    <t>2.63</t>
+  </si>
+  <si>
+    <t>TC-152</t>
+  </si>
+  <si>
+    <t>Search + Category + Duration triple-filter E2E flow</t>
+  </si>
+  <si>
+    <t>1.84</t>
+  </si>
+  <si>
+    <t>TC-153</t>
+  </si>
+  <si>
+    <t>Read single notification → verify badge decrements</t>
+  </si>
+  <si>
+    <t>TC-154</t>
+  </si>
+  <si>
+    <t>Settings Save → Redirect → Page reload E2E flow</t>
+  </si>
+  <si>
+    <t>4.16</t>
+  </si>
+  <si>
+    <t>TC-155</t>
+  </si>
+  <si>
+    <t>Full Regression: Reset → Login → CRUD → Profile → Settings → Logout</t>
+  </si>
+  <si>
+    <t>3.09</t>
+  </si>
+  <si>
+    <t>TC-156</t>
+  </si>
+  <si>
+    <t>Login page displays correctly on 360x800 mobile viewport</t>
+  </si>
+  <si>
+    <t>TC-157</t>
+  </si>
+  <si>
+    <t>Dashboard sidebar collapses on viewport &lt; 900px</t>
+  </si>
+  <si>
+    <t>3.86</t>
+  </si>
+  <si>
+    <t>TC-158</t>
+  </si>
+  <si>
+    <t>Mobile menu toggle shows/hides sidebar</t>
+  </si>
+  <si>
+    <t>3.43</t>
+  </si>
+  <si>
+    <t>TC-159</t>
+  </si>
+  <si>
+    <t>Dashboard stats grid wraps on narrow viewport</t>
+  </si>
+  <si>
+    <t>1.25</t>
+  </si>
+  <si>
+    <t>TC-160</t>
+  </si>
+  <si>
+    <t>Dashboard table horizontally scrollable on mobile</t>
+  </si>
+  <si>
+    <t>TC-161</t>
+  </si>
+  <si>
+    <t>Edit Workout form is fully usable on mobile viewport</t>
+  </si>
+  <si>
+    <t>TC-162</t>
+  </si>
+  <si>
+    <t>Profile page avatar and form stack vertically on mobile</t>
+  </si>
+  <si>
+    <t>1.88</t>
+  </si>
+  <si>
+    <t>TC-163</t>
+  </si>
+  <si>
+    <t>Settings form is readable and submittable on mobile</t>
+  </si>
+  <si>
+    <t>1.77</t>
+  </si>
+  <si>
+    <t>TC-164</t>
+  </si>
+  <si>
+    <t>Logout page centred and readable on all screen sizes</t>
+  </si>
+  <si>
+    <t>1.81</t>
+  </si>
+  <si>
+    <t>TC-165</t>
+  </si>
+  <si>
+    <t>Registration page is mobile-friendly</t>
+  </si>
+  <si>
+    <t>3.53</t>
+  </si>
+  <si>
+    <t>TC-166</t>
+  </si>
+  <si>
+    <t>Mobile: tap Dashboard nav link navigates correctly</t>
+  </si>
+  <si>
+    <t>4.29</t>
+  </si>
+  <si>
+    <t>TC-167</t>
+  </si>
+  <si>
+    <t>Mobile: tap Profile nav link navigates correctly</t>
+  </si>
+  <si>
+    <t>TC-168</t>
+  </si>
+  <si>
+    <t>Mobile: tap Settings nav link navigates correctly</t>
+  </si>
+  <si>
+    <t>2.95</t>
+  </si>
+  <si>
+    <t>TC-169</t>
+  </si>
+  <si>
+    <t>Mobile: tap Logout nav link navigates correctly</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>TC-170</t>
+  </si>
+  <si>
+    <t>Mobile: brand logo area visible in collapsed sidebar</t>
+  </si>
+  <si>
+    <t>3.62</t>
+  </si>
+  <si>
+    <t>TC-171</t>
+  </si>
+  <si>
+    <t>Mobile: back navigation returns to previous screen</t>
+  </si>
+  <si>
+    <t>3.61</t>
+  </si>
+  <si>
+    <t>TC-172</t>
+  </si>
+  <si>
+    <t>Mobile: swipe scroll on dashboard works smoothly</t>
+  </si>
+  <si>
+    <t>3.82</t>
+  </si>
+  <si>
+    <t>TC-173</t>
+  </si>
+  <si>
+    <t>Mobile: notification bell tappable and dropdown opens</t>
+  </si>
+  <si>
+    <t>3.94</t>
+  </si>
+  <si>
+    <t>TC-174</t>
+  </si>
+  <si>
+    <t>Mobile: edit workout button tappable in table row</t>
+  </si>
+  <si>
+    <t>1.95</t>
+  </si>
+  <si>
+    <t>TC-175</t>
+  </si>
+  <si>
+    <t>Mobile: delete workout confirmation dialog appears</t>
+  </si>
+  <si>
+    <t>3.95</t>
+  </si>
+  <si>
+    <t>TC-176</t>
+  </si>
+  <si>
+    <t>Mobile: create new workout using Add Exercise form</t>
+  </si>
+  <si>
+    <t>3.54</t>
+  </si>
+  <si>
+    <t>TC-177</t>
+  </si>
+  <si>
+    <t>Mobile: edit existing workout on edit form page</t>
+  </si>
+  <si>
+    <t>1.63</t>
+  </si>
+  <si>
+    <t>TC-178</t>
+  </si>
+  <si>
+    <t>Mobile: delete workout and verify removal</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>TC-179</t>
+  </si>
+  <si>
+    <t>Mobile: workout name input accepts text input on keyboard</t>
+  </si>
+  <si>
+    <t>TC-180</t>
+  </si>
+  <si>
+    <t>Mobile: category dropdown selection works</t>
+  </si>
+  <si>
+    <t>TC-181</t>
+  </si>
+  <si>
+    <t>Mobile: numeric keyboard shown for duration input</t>
+  </si>
+  <si>
+    <t>2.06</t>
+  </si>
+  <si>
+    <t>TC-182</t>
+  </si>
+  <si>
+    <t>Mobile: form scrolls to show inputs above keyboard</t>
+  </si>
+  <si>
+    <t>TC-183</t>
+  </si>
+  <si>
+    <t>Mobile: create workout with Cardio category</t>
+  </si>
+  <si>
+    <t>TC-184</t>
+  </si>
+  <si>
+    <t>Mobile: create workout with Strength category</t>
+  </si>
+  <si>
+    <t>1.53</t>
+  </si>
+  <si>
+    <t>TC-185</t>
+  </si>
+  <si>
+    <t>Mobile: create workout with Flexibility category</t>
+  </si>
+  <si>
+    <t>TC-186</t>
+  </si>
+  <si>
+    <t>Mobile: Login with valid credentials navigates to dashboard</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>TC-187</t>
+  </si>
+  <si>
+    <t>Mobile: Login with wrong password shows error page</t>
+  </si>
+  <si>
+    <t>TC-188</t>
+  </si>
+  <si>
+    <t>Mobile: Login form password field masks input</t>
+  </si>
+  <si>
+    <t>2.17</t>
+  </si>
+  <si>
+    <t>TC-189</t>
+  </si>
+  <si>
+    <t>Mobile: Login email keyboard type shown for email field</t>
+  </si>
+  <si>
+    <t>3.48</t>
+  </si>
+  <si>
+    <t>TC-190</t>
+  </si>
+  <si>
+    <t>Mobile: Login page has no horizontal scroll overflow</t>
+  </si>
+  <si>
+    <t>2.94</t>
+  </si>
+  <si>
+    <t>TC-191</t>
+  </si>
+  <si>
+    <t>Mobile: Profile update form is visible and submittable</t>
+  </si>
+  <si>
+    <t>TC-192</t>
+  </si>
+  <si>
+    <t>Mobile: Updated profile name shows in sidebar after save</t>
+  </si>
+  <si>
+    <t>TC-193</t>
+  </si>
+  <si>
+    <t>Mobile: Avatar upload button is tappable</t>
+  </si>
+  <si>
+    <t>3.90</t>
+  </si>
+  <si>
+    <t>TC-194</t>
+  </si>
+  <si>
+    <t>Mobile: Profile email field accepts valid email format</t>
+  </si>
+  <si>
+    <t>TC-195</t>
+  </si>
+  <si>
+    <t>Mobile: Profile page scrollable to reach phone field</t>
+  </si>
+  <si>
+    <t>TC-196</t>
+  </si>
+  <si>
+    <t>Mobile: Settings page renders all config rows</t>
+  </si>
+  <si>
+    <t>2.73</t>
+  </si>
+  <si>
+    <t>TC-197</t>
+  </si>
+  <si>
+    <t>Mobile: Settings dropdowns tappable and selectable</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>TC-198</t>
+  </si>
+  <si>
+    <t>Mobile: Settings Save button is tappable and submits</t>
+  </si>
+  <si>
+    <t>2.19</t>
+  </si>
+  <si>
+    <t>TC-199</t>
+  </si>
+  <si>
+    <t>Mobile: Settings Cancel button navigates to dashboard</t>
+  </si>
+  <si>
+    <t>4.40</t>
+  </si>
+  <si>
+    <t>TC-200</t>
+  </si>
+  <si>
+    <t>Mobile: Settings page has no layout overflow on small screens</t>
+  </si>
+  <si>
+    <t>4.23</t>
+  </si>
+  <si>
+    <t>TC-201</t>
+  </si>
+  <si>
+    <t>Business flow 1: Login → Add Workout → Search → Logout</t>
+  </si>
+  <si>
+    <t>TC-202</t>
+  </si>
+  <si>
+    <t>Business flow 2: Register Page Visit → Login → Dashboard Verify</t>
+  </si>
+  <si>
+    <t>2.47</t>
+  </si>
+  <si>
+    <t>TC-203</t>
+  </si>
+  <si>
+    <t>Business flow 3: Login → Edit Profile → Verify Sidebar Update</t>
+  </si>
+  <si>
+    <t>TC-204</t>
+  </si>
+  <si>
+    <t>Business flow 4: Login → File Upload → File Download</t>
+  </si>
+  <si>
+    <t>4.06</t>
+  </si>
+  <si>
+    <t>TC-205</t>
+  </si>
+  <si>
+    <t>Business flow 5: Login → CRUD cycle → Settings → Logout</t>
+  </si>
+  <si>
+    <t>2.23</t>
+  </si>
+  <si>
+    <t>TC-206</t>
+  </si>
+  <si>
+    <t>Business flow 6: Notification management full cycle</t>
+  </si>
+  <si>
+    <t>3.79</t>
+  </si>
+  <si>
+    <t>TC-207</t>
+  </si>
+  <si>
+    <t>Business flow 7: Registration to Operations and Logout</t>
+  </si>
+  <si>
+    <t>3.21</t>
+  </si>
+  <si>
+    <t>TC-208</t>
+  </si>
+  <si>
+    <t>Business flow 8: Search and Filter complete cycle</t>
+  </si>
+  <si>
+    <t>2.88</t>
+  </si>
+  <si>
+    <t>TC-209</t>
+  </si>
+  <si>
+    <t>Business flow 9: Avatar upload to profile verification</t>
+  </si>
+  <si>
+    <t>TC-210</t>
+  </si>
+  <si>
+    <t>Business flow 10: Reset state → full smoke test all pages</t>
+  </si>
+  <si>
+    <t>1.31</t>
+  </si>
+  <si>
+    <t>TC-211</t>
+  </si>
+  <si>
+    <t>Dashboard page load time under 3 seconds</t>
+  </si>
+  <si>
+    <t>TC-212</t>
+  </si>
+  <si>
+    <t>Login page load time under 2 seconds</t>
+  </si>
+  <si>
+    <t>TC-213</t>
+  </si>
+  <si>
+    <t>Create workout API responds within 500ms</t>
+  </si>
+  <si>
+    <t>TC-214</t>
+  </si>
+  <si>
+    <t>Search filter response time under 1 second</t>
+  </si>
+  <si>
+    <t>1.87</t>
+  </si>
+  <si>
+    <t>TC-215</t>
+  </si>
+  <si>
+    <t>File download responds within 2 seconds</t>
+  </si>
+  <si>
+    <t>4.91</t>
+  </si>
+  <si>
+    <t>TC-216</t>
+  </si>
+  <si>
+    <t>Notifications API responds within 300ms</t>
+  </si>
+  <si>
+    <t>1.57</t>
+  </si>
+  <si>
+    <t>TC-217</t>
+  </si>
+  <si>
+    <t>Profile update API responds within 500ms</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>TC-218</t>
+  </si>
+  <si>
+    <t>Delete workout API responds within 500ms</t>
+  </si>
+  <si>
+    <t>TC-219</t>
+  </si>
+  <si>
+    <t>Settings save API responds within 300ms</t>
+  </si>
+  <si>
+    <t>4.39</t>
+  </si>
+  <si>
+    <t>TC-220</t>
+  </si>
+  <si>
+    <t>Application server starts without error</t>
+  </si>
+  <si>
+    <t>2.48</t>
+  </si>
+  <si>
+    <t>TC-221</t>
+  </si>
+  <si>
+    <t>Login form has correct placeholder text</t>
+  </si>
+  <si>
+    <t>TC-222</t>
+  </si>
+  <si>
+    <t>Register form has all required field labels</t>
+  </si>
+  <si>
+    <t>4.74</t>
+  </si>
+  <si>
+    <t>TC-223</t>
+  </si>
+  <si>
+    <t>Dashboard workout table has correct column headers</t>
+  </si>
+  <si>
+    <t>TC-224</t>
+  </si>
+  <si>
+    <t>Workout ID formatted as WK-001 etc. in table</t>
+  </si>
+  <si>
+    <t>TC-225</t>
+  </si>
+  <si>
+    <t>Dashboard stats cards all have correct labels</t>
+  </si>
+  <si>
+    <t>TC-226</t>
+  </si>
+  <si>
+    <t>Sidebar brand name 'Fitwave' is visible</t>
+  </si>
+  <si>
+    <t>TC-227</t>
+  </si>
+  <si>
+    <t>Profile avatar placeholder initials 'HV' visible</t>
+  </si>
+  <si>
+    <t>TC-228</t>
+  </si>
+  <si>
+    <t>Settings page shows all three configuration option rows</t>
+  </si>
+  <si>
+    <t>TC-229</t>
+  </si>
+  <si>
+    <t>Edit workout form pre-fills all three existing field values</t>
+  </si>
+  <si>
+    <t>TC-230</t>
+  </si>
+  <si>
+    <t>Upload success back button visible and labelled correctly</t>
+  </si>
+  <si>
+    <t>TC-231</t>
+  </si>
+  <si>
+    <t>Workout duration displayed with 'mins' suffix in table</t>
+  </si>
+  <si>
+    <t>3.72</t>
+  </si>
+  <si>
+    <t>TC-232</t>
+  </si>
+  <si>
+    <t>Category badge displayed inline in workout row</t>
+  </si>
+  <si>
+    <t>4.96</t>
+  </si>
+  <si>
+    <t>TC-233</t>
+  </si>
+  <si>
+    <t>Total minutes stat sums all workout durations correctly</t>
+  </si>
+  <si>
+    <t>TC-234</t>
+  </si>
+  <si>
+    <t>Active workouts count matches actual table row count</t>
+  </si>
+  <si>
+    <t>1.03</t>
+  </si>
+  <si>
+    <t>TC-235</t>
+  </si>
+  <si>
+    <t>Notification message text correct for default notification 1</t>
+  </si>
+  <si>
+    <t>3.70</t>
+  </si>
+  <si>
+    <t>TC-236</t>
+  </si>
+  <si>
+    <t>Notification message text correct for default notification 2</t>
+  </si>
+  <si>
+    <t>2.25</t>
+  </si>
+  <si>
+    <t>TC-237</t>
+  </si>
+  <si>
+    <t>Default user email shown correctly on profile page</t>
+  </si>
+  <si>
+    <t>2.30</t>
+  </si>
+  <si>
+    <t>TC-238</t>
+  </si>
+  <si>
+    <t>Default user phone shown correctly on profile page</t>
+  </si>
+  <si>
+    <t>TC-239</t>
+  </si>
+  <si>
+    <t>Backup JSON has correct structure with id, name, category, duration</t>
   </si>
   <si>
     <t>1.29</t>
   </si>
   <si>
-    <t>TC-004</t>
-  </si>
-  <si>
-    <t>Login with SQL Injection string in username field</t>
-  </si>
-  <si>
-    <t>4.63</t>
-  </si>
-  <si>
-    <t>TC-005</t>
-  </si>
-  <si>
-    <t>Login with empty email address field</t>
-  </si>
-  <si>
-    <t>3.59</t>
-  </si>
-  <si>
-    <t>TC-006</t>
-  </si>
-  <si>
-    <t>Login with empty password field</t>
-  </si>
-  <si>
-    <t>4.13</t>
-  </si>
-  <si>
-    <t>TC-007</t>
-  </si>
-  <si>
-    <t>Login with malformed email structure (missing @)</t>
-  </si>
-  <si>
-    <t>3.55</t>
-  </si>
-  <si>
-    <t>TC-008</t>
-  </si>
-  <si>
-    <t>Login case sensitivity verification on email parameter</t>
-  </si>
-  <si>
-    <t>3.41</t>
-  </si>
-  <si>
-    <t>TC-009</t>
-  </si>
-  <si>
-    <t>Register new account with complex password rules</t>
-  </si>
-  <si>
-    <t>3.56</t>
-  </si>
-  <si>
-    <t>TC-010</t>
-  </si>
-  <si>
-    <t>Register with simple/short password (under 8 chars)</t>
-  </si>
-  <si>
-    <t>3.70</t>
-  </si>
-  <si>
-    <t>TC-011</t>
-  </si>
-  <si>
-    <t>Register with password lacking uppercase letters complexity rules</t>
-  </si>
-  <si>
-    <t>3.68</t>
-  </si>
-  <si>
-    <t>TC-012</t>
-  </si>
-  <si>
-    <t>Register with password lacking numeric values</t>
-  </si>
-  <si>
-    <t>1.47</t>
-  </si>
-  <si>
-    <t>TC-013</t>
-  </si>
-  <si>
-    <t>Register with empty name inputs</t>
-  </si>
-  <si>
-    <t>1.16</t>
-  </si>
-  <si>
-    <t>TC-014</t>
-  </si>
-  <si>
-    <t>Register with invalid email format</t>
-  </si>
-  <si>
-    <t>1.42</t>
-  </si>
-  <si>
-    <t>TC-015</t>
-  </si>
-  <si>
-    <t>Register screen redirects back to Sign In page check</t>
-  </si>
-  <si>
-    <t>4.91</t>
-  </si>
-  <si>
-    <t>TC-016</t>
-  </si>
-  <si>
-    <t>Register account with extremely long name value</t>
-  </si>
-  <si>
-    <t>1.87</t>
-  </si>
-  <si>
-    <t>TC-017</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 1</t>
-  </si>
-  <si>
-    <t>4.03</t>
-  </si>
-  <si>
-    <t>TC-018</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 2</t>
-  </si>
-  <si>
-    <t>TC-019</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 3</t>
-  </si>
-  <si>
-    <t>3.92</t>
-  </si>
-  <si>
-    <t>TC-020</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 4</t>
+    <t>TC-240</t>
+  </si>
+  <si>
+    <t>Created workout appears in correct position in table</t>
+  </si>
+  <si>
+    <t>2.49</t>
+  </si>
+  <si>
+    <t>TC-241</t>
+  </si>
+  <si>
+    <t>Login form inputs have associated label elements</t>
+  </si>
+  <si>
+    <t>2.83</t>
+  </si>
+  <si>
+    <t>TC-242</t>
+  </si>
+  <si>
+    <t>All buttons have descriptive visible text or IDs</t>
+  </si>
+  <si>
+    <t>TC-243</t>
+  </si>
+  <si>
+    <t>Dashboard page has single H1 tag</t>
+  </si>
+  <si>
+    <t>TC-244</t>
+  </si>
+  <si>
+    <t>Pages have valid HTML lang attribute set</t>
+  </si>
+  <si>
+    <t>TC-245</t>
+  </si>
+  <si>
+    <t>Viewport meta tag present for mobile rendering</t>
+  </si>
+  <si>
+    <t>TC-246</t>
+  </si>
+  <si>
+    <t>Mobile tap targets are minimum 44x44px</t>
+  </si>
+  <si>
+    <t>3.05</t>
+  </si>
+  <si>
+    <t>TC-247</t>
+  </si>
+  <si>
+    <t>Mobile text is readable without zooming (min 14px)</t>
+  </si>
+  <si>
+    <t>3.87</t>
+  </si>
+  <si>
+    <t>TC-248</t>
+  </si>
+  <si>
+    <t>Form submit buttons respond to keyboard Enter key</t>
+  </si>
+  <si>
+    <t>TC-249</t>
+  </si>
+  <si>
+    <t>Error messages are visible and descriptive</t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t>TC-250</t>
+  </si>
+  <si>
+    <t>Links have href attributes set correctly</t>
+  </si>
+  <si>
+    <t>TC-251</t>
+  </si>
+  <si>
+    <t>Login page does not expose server technology in headers</t>
+  </si>
+  <si>
+    <t>TC-252</t>
+  </si>
+  <si>
+    <t>Login error page does not reflect XSS payload</t>
+  </si>
+  <si>
+    <t>2.78</t>
+  </si>
+  <si>
+    <t>TC-253</t>
+  </si>
+  <si>
+    <t>SQL injection in login username field is blocked</t>
+  </si>
+  <si>
+    <t>3.51</t>
+  </si>
+  <si>
+    <t>TC-254</t>
+  </si>
+  <si>
+    <t>Uploaded files saved with timestamp prefix not original name</t>
+  </si>
+  <si>
+    <t>TC-255</t>
+  </si>
+  <si>
+    <t>Dashboard XSS in search param is escaped in output</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>TC-256</t>
+  </si>
+  <si>
+    <t>Profile update XSS payload escaped on profile page render</t>
+  </si>
+  <si>
+    <t>1.96</t>
+  </si>
+  <si>
+    <t>TC-257</t>
+  </si>
+  <si>
+    <t>Login redirect Location header is relative path only</t>
+  </si>
+  <si>
+    <t>1.09</t>
+  </si>
+  <si>
+    <t>TC-258</t>
+  </si>
+  <si>
+    <t>Registration error page does not leak stack trace</t>
+  </si>
+  <si>
+    <t>2.97</t>
+  </si>
+  <si>
+    <t>TC-259</t>
+  </si>
+  <si>
+    <t>Login 401 error page does not reveal server internals</t>
+  </si>
+  <si>
+    <t>TC-260</t>
+  </si>
+  <si>
+    <t>Non-existent route returns 404 not 500</t>
+  </si>
+  <si>
+    <t>3.22</t>
+  </si>
+  <si>
+    <t>TC-261</t>
+  </si>
+  <si>
+    <t>POST /api/notifications/clear returns JSON {success:true}</t>
+  </si>
+  <si>
+    <t>2.65</t>
+  </si>
+  <si>
+    <t>TC-262</t>
+  </si>
+  <si>
+    <t>POST /api/notifications/read/:id returns JSON {success:true}</t>
+  </si>
+  <si>
+    <t>TC-263</t>
+  </si>
+  <si>
+    <t>GET /download/backup returns valid JSON array</t>
+  </si>
+  <si>
+    <t>TC-264</t>
+  </si>
+  <si>
+    <t>POST /login returns 302 with Location header on success</t>
+  </si>
+  <si>
+    <t>TC-265</t>
+  </si>
+  <si>
+    <t>POST /register returns 200 on valid submission</t>
+  </si>
+  <si>
+    <t>2.61</t>
+  </si>
+  <si>
+    <t>TC-266</t>
+  </si>
+  <si>
+    <t>GET /dashboard returns 200 with HTML content</t>
+  </si>
+  <si>
+    <t>4.87</t>
+  </si>
+  <si>
+    <t>TC-267</t>
+  </si>
+  <si>
+    <t>POST /workout/create returns 302 redirect</t>
+  </si>
+  <si>
+    <t>TC-268</t>
+  </si>
+  <si>
+    <t>POST /workout/delete/:id returns 302 redirect</t>
+  </si>
+  <si>
+    <t>2.89</t>
+  </si>
+  <si>
+    <t>TC-269</t>
+  </si>
+  <si>
+    <t>POST /settings/save returns 302 redirect to /settings</t>
+  </si>
+  <si>
+    <t>TC-270</t>
+  </si>
+  <si>
+    <t>GET /workout/edit/:id 404 for non-existent workout</t>
+  </si>
+  <si>
+    <t>TC-271</t>
+  </si>
+  <si>
+    <t>Workout list state persists across multiple dashboard loads</t>
+  </si>
+  <si>
+    <t>TC-272</t>
+  </si>
+  <si>
+    <t>Create workout – state shared between requests</t>
+  </si>
+  <si>
+    <t>TC-273</t>
+  </si>
+  <si>
+    <t>Delete workout – state updated immediately</t>
+  </si>
+  <si>
+    <t>TC-274</t>
+  </si>
+  <si>
+    <t>Profile update persists to next GET /profile request</t>
+  </si>
+  <si>
+    <t>TC-275</t>
+  </si>
+  <si>
+    <t>Notifications cleared – state persists to next dashboard load</t>
+  </si>
+  <si>
+    <t>TC-276</t>
+  </si>
+  <si>
+    <t>Edit workout change visible in backup JSON immediately</t>
+  </si>
+  <si>
+    <t>3.78</t>
+  </si>
+  <si>
+    <t>TC-277</t>
+  </si>
+  <si>
+    <t>Reset endpoint fully restores all in-memory state</t>
   </si>
   <si>
     <t>4.44</t>
   </si>
   <si>
-    <t>TC-021</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 5</t>
-  </si>
-  <si>
-    <t>4.00</t>
-  </si>
-  <si>
-    <t>TC-022</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 6</t>
-  </si>
-  <si>
-    <t>2.65</t>
-  </si>
-  <si>
-    <t>TC-023</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 7</t>
-  </si>
-  <si>
-    <t>2.05</t>
-  </si>
-  <si>
-    <t>TC-024</t>
-  </si>
-  <si>
-    <t>Dashboard UI element presence check case 8</t>
-  </si>
-  <si>
-    <t>1.56</t>
-  </si>
-  <si>
-    <t>TC-025</t>
-  </si>
-  <si>
-    <t>Update profile details check case 1</t>
+    <t>TC-278</t>
+  </si>
+  <si>
+    <t>Avatar upload path persists on subsequent profile loads</t>
+  </si>
+  <si>
+    <t>TC-279</t>
+  </si>
+  <si>
+    <t>Multiple sequential profile updates – last write wins</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>TC-280</t>
+  </si>
+  <si>
+    <t>Notification read state removed from array permanently</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>TC-281</t>
+  </si>
+  <si>
+    <t>Dashboard with 100 workouts renders without crash</t>
+  </si>
+  <si>
+    <t>4.27</t>
+  </si>
+  <si>
+    <t>TC-282</t>
+  </si>
+  <si>
+    <t>Create workout with special characters in name (&amp; &lt; &gt;)</t>
+  </si>
+  <si>
+    <t>TC-283</t>
+  </si>
+  <si>
+    <t>Edit workout with same values as existing – no change</t>
+  </si>
+  <si>
+    <t>2.98</t>
+  </si>
+  <si>
+    <t>TC-284</t>
+  </si>
+  <si>
+    <t>Delete same workout twice – second delete is silent no-op</t>
+  </si>
+  <si>
+    <t>TC-285</t>
+  </si>
+  <si>
+    <t>Upload file then immediately download backup – state intact</t>
+  </si>
+  <si>
+    <t>TC-286</t>
+  </si>
+  <si>
+    <t>Create workout with duration at max int (99999)</t>
+  </si>
+  <si>
+    <t>3.98</t>
+  </si>
+  <si>
+    <t>TC-287</t>
+  </si>
+  <si>
+    <t>Profile name with emoji stored and retrieved</t>
+  </si>
+  <si>
+    <t>TC-288</t>
+  </si>
+  <si>
+    <t>Search with URL-encoded space (%20) as query</t>
+  </si>
+  <si>
+    <t>2.62</t>
+  </si>
+  <si>
+    <t>TC-289</t>
+  </si>
+  <si>
+    <t>All filter params empty string – shows all workouts</t>
   </si>
   <si>
     <t>3.44</t>
   </si>
   <si>
-    <t>TC-026</t>
-  </si>
-  <si>
-    <t>Update profile details check case 2</t>
-  </si>
-  <si>
-    <t>4.60</t>
-  </si>
-  <si>
-    <t>TC-027</t>
-  </si>
-  <si>
-    <t>Update profile details check case 3</t>
-  </si>
-  <si>
-    <t>TC-028</t>
-  </si>
-  <si>
-    <t>Update profile details check case 4</t>
-  </si>
-  <si>
-    <t>1.27</t>
-  </si>
-  <si>
-    <t>TC-029</t>
-  </si>
-  <si>
-    <t>Update profile details check case 5</t>
-  </si>
-  <si>
-    <t>4.07</t>
-  </si>
-  <si>
-    <t>TC-030</t>
-  </si>
-  <si>
-    <t>Update profile details check case 6</t>
-  </si>
-  <si>
-    <t>1.78</t>
-  </si>
-  <si>
-    <t>TC-031</t>
-  </si>
-  <si>
-    <t>Update profile details check case 7</t>
-  </si>
-  <si>
-    <t>2.01</t>
-  </si>
-  <si>
-    <t>TC-032</t>
-  </si>
-  <si>
-    <t>Update profile details check case 8</t>
-  </si>
-  <si>
-    <t>1.24</t>
-  </si>
-  <si>
-    <t>TC-033</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 1</t>
-  </si>
-  <si>
-    <t>1.72</t>
-  </si>
-  <si>
-    <t>TC-034</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 2</t>
-  </si>
-  <si>
-    <t>2.22</t>
-  </si>
-  <si>
-    <t>TC-035</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 3</t>
-  </si>
-  <si>
-    <t>4.36</t>
-  </si>
-  <si>
-    <t>TC-036</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 4</t>
-  </si>
-  <si>
-    <t>4.82</t>
-  </si>
-  <si>
-    <t>TC-037</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 5</t>
-  </si>
-  <si>
-    <t>4.42</t>
-  </si>
-  <si>
-    <t>TC-038</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 6</t>
-  </si>
-  <si>
-    <t>1.92</t>
-  </si>
-  <si>
-    <t>TC-039</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 7</t>
-  </si>
-  <si>
-    <t>4.09</t>
-  </si>
-  <si>
-    <t>TC-040</t>
-  </si>
-  <si>
-    <t>Save settings configurations check case 8</t>
-  </si>
-  <si>
-    <t>4.61</t>
-  </si>
-  <si>
-    <t>TC-041</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Cardio"</t>
-  </si>
-  <si>
-    <t>TC-042</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Squat"</t>
-  </si>
-  <si>
-    <t>3.80</t>
-  </si>
-  <si>
-    <t>TC-043</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Yoga"</t>
-  </si>
-  <si>
-    <t>1.32</t>
-  </si>
-  <si>
-    <t>TC-044</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Morning"</t>
-  </si>
-  <si>
-    <t>2.44</t>
-  </si>
-  <si>
-    <t>TC-045</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Heavy"</t>
-  </si>
-  <si>
-    <t>2.25</t>
-  </si>
-  <si>
-    <t>TC-046</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Blast"</t>
-  </si>
-  <si>
-    <t>2.86</t>
-  </si>
-  <si>
-    <t>TC-047</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Session"</t>
-  </si>
-  <si>
-    <t>TC-048</t>
-  </si>
-  <si>
-    <t>Search exercises matching term "Flow"</t>
-  </si>
-  <si>
-    <t>4.80</t>
-  </si>
-  <si>
-    <t>TC-049</t>
-  </si>
-  <si>
-    <t>Filter workout exercises by category: "Cardio"</t>
-  </si>
-  <si>
-    <t>TC-050</t>
-  </si>
-  <si>
-    <t>Filter workout exercises by category: "Strength"</t>
-  </si>
-  <si>
-    <t>3.65</t>
-  </si>
-  <si>
-    <t>TC-051</t>
-  </si>
-  <si>
-    <t>Filter workout exercises by category: "Flexibility"</t>
-  </si>
-  <si>
-    <t>1.68</t>
-  </si>
-  <si>
-    <t>TC-052</t>
-  </si>
-  <si>
-    <t>2.80</t>
-  </si>
-  <si>
-    <t>TC-053</t>
-  </si>
-  <si>
-    <t>1.53</t>
-  </si>
-  <si>
-    <t>TC-054</t>
-  </si>
-  <si>
-    <t>2.67</t>
-  </si>
-  <si>
-    <t>TC-055</t>
-  </si>
-  <si>
-    <t>2.37</t>
-  </si>
-  <si>
-    <t>TC-056</t>
-  </si>
-  <si>
-    <t>4.87</t>
-  </si>
-  <si>
-    <t>TC-057</t>
-  </si>
-  <si>
-    <t>Create routine record operation test case 1</t>
-  </si>
-  <si>
-    <t>1.26</t>
-  </si>
-  <si>
-    <t>TC-058</t>
-  </si>
-  <si>
-    <t>Create routine record operation test case 2</t>
-  </si>
-  <si>
-    <t>1.52</t>
-  </si>
-  <si>
-    <t>TC-059</t>
-  </si>
-  <si>
-    <t>Create routine record operation test case 3</t>
-  </si>
-  <si>
-    <t>2.58</t>
-  </si>
-  <si>
-    <t>TC-060</t>
-  </si>
-  <si>
-    <t>Create routine record operation test case 4</t>
-  </si>
-  <si>
-    <t>4.99</t>
-  </si>
-  <si>
-    <t>TC-061</t>
-  </si>
-  <si>
-    <t>Update routine record operation test case 5</t>
-  </si>
-  <si>
-    <t>4.70</t>
-  </si>
-  <si>
-    <t>TC-062</t>
-  </si>
-  <si>
-    <t>Update routine record operation test case 6</t>
-  </si>
-  <si>
-    <t>TC-063</t>
-  </si>
-  <si>
-    <t>Update routine record operation test case 7</t>
-  </si>
-  <si>
-    <t>4.89</t>
-  </si>
-  <si>
-    <t>TC-064</t>
-  </si>
-  <si>
-    <t>Update routine record operation test case 8</t>
-  </si>
-  <si>
-    <t>3.38</t>
-  </si>
-  <si>
-    <t>TC-065</t>
-  </si>
-  <si>
-    <t>Delete routine record operation test case 9</t>
-  </si>
-  <si>
-    <t>TC-066</t>
-  </si>
-  <si>
-    <t>Delete routine record operation test case 10</t>
-  </si>
-  <si>
-    <t>3.78</t>
-  </si>
-  <si>
-    <t>TC-067</t>
-  </si>
-  <si>
-    <t>Delete routine record operation test case 11</t>
-  </si>
-  <si>
-    <t>2.27</t>
-  </si>
-  <si>
-    <t>TC-068</t>
-  </si>
-  <si>
-    <t>Delete routine record operation test case 12</t>
-  </si>
-  <si>
-    <t>2.54</t>
-  </si>
-  <si>
-    <t>TC-069</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 1</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
-    <t>TC-070</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 2</t>
-  </si>
-  <si>
-    <t>3.40</t>
-  </si>
-  <si>
-    <t>TC-071</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 3</t>
-  </si>
-  <si>
-    <t>1.03</t>
-  </si>
-  <si>
-    <t>TC-072</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 4</t>
-  </si>
-  <si>
-    <t>4.01</t>
-  </si>
-  <si>
-    <t>TC-073</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 5</t>
-  </si>
-  <si>
-    <t>3.19</t>
-  </si>
-  <si>
-    <t>TC-074</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 6</t>
-  </si>
-  <si>
-    <t>3.30</t>
-  </si>
-  <si>
-    <t>TC-075</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 7</t>
-  </si>
-  <si>
-    <t>4.59</t>
-  </si>
-  <si>
-    <t>TC-076</t>
-  </si>
-  <si>
-    <t>Upload exercise template tracker document scenario 8</t>
-  </si>
-  <si>
-    <t>1.88</t>
-  </si>
-  <si>
-    <t>TC-077</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 1: check report or backup URL</t>
-  </si>
-  <si>
-    <t>2.94</t>
-  </si>
-  <si>
-    <t>TC-078</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 2: check report or backup URL</t>
-  </si>
-  <si>
-    <t>3.27</t>
-  </si>
-  <si>
-    <t>TC-079</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 3: check report or backup URL</t>
-  </si>
-  <si>
-    <t>TC-080</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 4: check report or backup URL</t>
-  </si>
-  <si>
-    <t>2.53</t>
-  </si>
-  <si>
-    <t>TC-081</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 5: check report or backup URL</t>
-  </si>
-  <si>
-    <t>2.64</t>
-  </si>
-  <si>
-    <t>TC-082</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 6: check report or backup URL</t>
+    <t>TC-290</t>
+  </si>
+  <si>
+    <t>Notification badge updates correctly after partial read</t>
+  </si>
+  <si>
+    <t>TC-291</t>
+  </si>
+  <si>
+    <t>Regression: After edit, original workout not duplicated</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>TC-292</t>
+  </si>
+  <si>
+    <t>Regression: Delete last workout then create new – ID correct</t>
+  </si>
+  <si>
+    <t>1.49</t>
+  </si>
+  <si>
+    <t>TC-293</t>
+  </si>
+  <si>
+    <t>Regression: Profile update does not affect workout list</t>
+  </si>
+  <si>
+    <t>2.85</t>
+  </si>
+  <si>
+    <t>TC-294</t>
+  </si>
+  <si>
+    <t>Regression: Settings save does not clear notifications</t>
+  </si>
+  <si>
+    <t>1.15</t>
+  </si>
+  <si>
+    <t>TC-295</t>
+  </si>
+  <si>
+    <t>Regression: File upload does not alter workout state</t>
+  </si>
+  <si>
+    <t>2.87</t>
+  </si>
+  <si>
+    <t>TC-296</t>
+  </si>
+  <si>
+    <t>Regression: Notification clear does not affect workout list</t>
   </si>
   <si>
     <t>2.11</t>
   </si>
   <si>
-    <t>TC-083</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 7: check report or backup URL</t>
-  </si>
-  <si>
-    <t>2.50</t>
-  </si>
-  <si>
-    <t>TC-084</t>
-  </si>
-  <si>
-    <t>Download file payload scenario 8: check report or backup URL</t>
-  </si>
-  <si>
-    <t>TC-085</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 1 as read</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>TC-086</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 2 as read</t>
-  </si>
-  <si>
-    <t>3.34</t>
-  </si>
-  <si>
-    <t>TC-087</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 3 as read</t>
-  </si>
-  <si>
-    <t>TC-088</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 4 as read</t>
-  </si>
-  <si>
-    <t>TC-089</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 5 as read</t>
-  </si>
-  <si>
-    <t>2.20</t>
-  </si>
-  <si>
-    <t>TC-090</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 6 as read</t>
-  </si>
-  <si>
-    <t>4.64</t>
-  </si>
-  <si>
-    <t>TC-091</t>
-  </si>
-  <si>
-    <t>Mark notification item ID 7 as read</t>
-  </si>
-  <si>
-    <t>4.12</t>
-  </si>
-  <si>
-    <t>TC-092</t>
-  </si>
-  <si>
-    <t>Clear all panel notifications</t>
-  </si>
-  <si>
-    <t>4.10</t>
-  </si>
-  <si>
-    <t>TC-093</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 1</t>
-  </si>
-  <si>
-    <t>1.77</t>
-  </si>
-  <si>
-    <t>TC-094</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 2</t>
-  </si>
-  <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>TC-095</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 3</t>
-  </si>
-  <si>
-    <t>4.75</t>
-  </si>
-  <si>
-    <t>TC-096</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 4</t>
-  </si>
-  <si>
-    <t>2.77</t>
-  </si>
-  <si>
-    <t>TC-097</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 5</t>
-  </si>
-  <si>
-    <t>2.06</t>
-  </si>
-  <si>
-    <t>TC-098</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 6</t>
-  </si>
-  <si>
-    <t>2.85</t>
-  </si>
-  <si>
-    <t>TC-099</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 7</t>
-  </si>
-  <si>
-    <t>3.98</t>
-  </si>
-  <si>
-    <t>TC-100</t>
-  </si>
-  <si>
-    <t>Generate weekly activities visual summary scenario 8</t>
-  </si>
-  <si>
-    <t>4.52</t>
-  </si>
-  <si>
-    <t>TC-101</t>
-  </si>
-  <si>
-    <t>Logout user session session termination scenario 1</t>
-  </si>
-  <si>
-    <t>2.60</t>
-  </si>
-  <si>
-    <t>TC-102</t>
-  </si>
-  <si>
-    <t>Logout user session session termination scenario 2</t>
-  </si>
-  <si>
-    <t>3.18</t>
-  </si>
-  <si>
-    <t>TC-103</t>
-  </si>
-  <si>
-    <t>Logout user session session termination scenario 3</t>
-  </si>
-  <si>
-    <t>4.27</t>
-  </si>
-  <si>
-    <t>TC-104</t>
-  </si>
-  <si>
-    <t>Logout user session session termination scenario 4</t>
-  </si>
-  <si>
-    <t>4.77</t>
-  </si>
-  <si>
-    <t>TC-105</t>
-  </si>
-  <si>
-    <t>Logout user session session termination scenario 5</t>
-  </si>
-  <si>
-    <t>4.31</t>
-  </si>
-  <si>
-    <t>TC-106</t>
-  </si>
-  <si>
-    <t>Inject script HTML tag in registration form name input</t>
-  </si>
-  <si>
-    <t>2.36</t>
-  </si>
-  <si>
-    <t>TC-107</t>
-  </si>
-  <si>
-    <t>Inject iframe tags in profile details email input</t>
-  </si>
-  <si>
-    <t>3.88</t>
-  </si>
-  <si>
-    <t>TC-108</t>
-  </si>
-  <si>
-    <t>Attempt SQL injection payload in Login username text input</t>
-  </si>
-  <si>
-    <t>2.18</t>
-  </si>
-  <si>
-    <t>TC-109</t>
-  </si>
-  <si>
-    <t>Verify registration weak password rules rejection</t>
-  </si>
-  <si>
-    <t>1.99</t>
-  </si>
-  <si>
-    <t>TC-110</t>
-  </si>
-  <si>
-    <t>Register with complexity missing digit requirement validation</t>
-  </si>
-  <si>
-    <t>3.84</t>
-  </si>
-  <si>
-    <t>TC-111</t>
-  </si>
-  <si>
-    <t>Register with complexity missing special characters requirement validation</t>
-  </si>
-  <si>
-    <t>TC-112</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 1280x800 (Desktop resolution layout check)</t>
-  </si>
-  <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>TC-113</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 1024x768 (Laptop/Large tablet resolution layout check)</t>
-  </si>
-  <si>
-    <t>1.41</t>
-  </si>
-  <si>
-    <t>TC-114</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 768x1024 (Medium tablet vertical viewport check)</t>
-  </si>
-  <si>
-    <t>3.87</t>
-  </si>
-  <si>
-    <t>TC-115</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 375x812 (Mobile portrait resolution layout check)</t>
-  </si>
-  <si>
-    <t>4.05</t>
-  </si>
-  <si>
-    <t>TC-116</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 414x896 (Large mobile portrait viewport check)</t>
-  </si>
-  <si>
-    <t>1.93</t>
-  </si>
-  <si>
-    <t>TC-117</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 320x568 (Small mobile screen resolution check)</t>
-  </si>
-  <si>
-    <t>1.85</t>
-  </si>
-  <si>
-    <t>TC-118</t>
-  </si>
-  <si>
-    <t>Validate UI layouts under viewport: 1440x900 (Ultra-wide desktop screen check)</t>
-  </si>
-  <si>
-    <t>1.33</t>
-  </si>
-  <si>
-    <t>TC-119</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 1: User Registration to Operations and Logout</t>
-  </si>
-  <si>
-    <t>TC-120</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 2: User Registration to Operations and Logout</t>
-  </si>
-  <si>
-    <t>TC-121</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 3: User Registration to Operations and Logout</t>
-  </si>
-  <si>
-    <t>3.43</t>
-  </si>
-  <si>
-    <t>TC-122</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 4: User Registration to Operations and Logout</t>
-  </si>
-  <si>
-    <t>TC-123</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 5: User Registration to Operations and Logout</t>
-  </si>
-  <si>
-    <t>1.06</t>
-  </si>
-  <si>
-    <t>TC-124</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 6: User Registration to Operations and Logout</t>
-  </si>
-  <si>
-    <t>1.00</t>
-  </si>
-  <si>
-    <t>TC-125</t>
-  </si>
-  <si>
-    <t>Complete End-to-End Business Scenario Flow 7: User Registration to Operations and Logout</t>
+    <t>TC-297</t>
+  </si>
+  <si>
+    <t>Regression: Total minutes stat correct after edit operation</t>
+  </si>
+  <si>
+    <t>3.66</t>
+  </si>
+  <si>
+    <t>TC-298</t>
+  </si>
+  <si>
+    <t>Regression: Search still works correctly after CRUD operations</t>
+  </si>
+  <si>
+    <t>4.54</t>
+  </si>
+  <si>
+    <t>TC-299</t>
+  </si>
+  <si>
+    <t>Regression: Avatar upload does not break profile form fields</t>
+  </si>
+  <si>
+    <t>4.14</t>
+  </si>
+  <si>
+    <t>TC-300</t>
+  </si>
+  <si>
+    <t>Regression: Complete 300-case smoke – all routes return expected codes</t>
+  </si>
+  <si>
+    <t>1.67</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1847,7 +3227,7 @@
         <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>9</v>
@@ -1855,16 +3235,16 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>9</v>
@@ -1872,16 +3252,16 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>9</v>
@@ -2000,7 +3380,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>9</v>
@@ -2008,16 +3388,16 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>9</v>
@@ -2025,16 +3405,16 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>9</v>
@@ -2042,16 +3422,16 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>9</v>
@@ -2059,16 +3439,16 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>9</v>
@@ -2076,16 +3456,16 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>9</v>
@@ -2093,16 +3473,16 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>9</v>
@@ -2110,16 +3490,16 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>9</v>
@@ -2127,16 +3507,16 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>9</v>
@@ -2144,16 +3524,16 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>9</v>
@@ -2161,16 +3541,16 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>9</v>
@@ -2178,16 +3558,16 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>9</v>
@@ -2238,7 +3618,7 @@
         <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>9</v>
@@ -2246,16 +3626,16 @@
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>9</v>
@@ -2263,16 +3643,16 @@
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>9</v>
@@ -2280,16 +3660,16 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>9</v>
@@ -2297,16 +3677,16 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>9</v>
@@ -2314,16 +3694,16 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>9</v>
@@ -2331,16 +3711,16 @@
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>9</v>
@@ -2348,16 +3728,16 @@
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>9</v>
@@ -2365,16 +3745,16 @@
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>9</v>
@@ -2382,16 +3762,16 @@
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>151</v>
+        <v>12</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>9</v>
@@ -2399,16 +3779,16 @@
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>9</v>
@@ -2416,16 +3796,16 @@
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>9</v>
@@ -2433,16 +3813,16 @@
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>9</v>
@@ -2450,16 +3830,16 @@
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>9</v>
@@ -2467,16 +3847,16 @@
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>9</v>
@@ -2484,16 +3864,16 @@
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>9</v>
@@ -2501,16 +3881,16 @@
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>9</v>
@@ -2518,16 +3898,16 @@
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>9</v>
@@ -2535,16 +3915,16 @@
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>9</v>
@@ -2552,16 +3932,16 @@
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>9</v>
@@ -2569,16 +3949,16 @@
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>9</v>
@@ -2586,16 +3966,16 @@
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>112</v>
+        <v>188</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>9</v>
@@ -2603,16 +3983,16 @@
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>9</v>
@@ -2620,16 +4000,16 @@
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>9</v>
@@ -2637,16 +4017,16 @@
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>9</v>
@@ -2654,16 +4034,16 @@
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>9</v>
@@ -2671,16 +4051,16 @@
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>9</v>
@@ -2688,16 +4068,16 @@
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>9</v>
@@ -2705,16 +4085,16 @@
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>9</v>
@@ -2722,16 +4102,16 @@
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>9</v>
@@ -2739,16 +4119,16 @@
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>9</v>
@@ -2756,16 +4136,16 @@
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>9</v>
@@ -2773,16 +4153,16 @@
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>9</v>
@@ -2790,16 +4170,16 @@
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>9</v>
@@ -2807,16 +4187,16 @@
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>9</v>
@@ -2824,16 +4204,16 @@
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>9</v>
@@ -2841,16 +4221,16 @@
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>9</v>
@@ -2858,16 +4238,16 @@
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>9</v>
@@ -2875,16 +4255,16 @@
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>216</v>
+        <v>133</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>9</v>
@@ -2892,16 +4272,16 @@
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>9</v>
@@ -2909,16 +4289,16 @@
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>9</v>
@@ -2926,16 +4306,16 @@
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>9</v>
@@ -2943,16 +4323,16 @@
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>9</v>
@@ -2960,16 +4340,16 @@
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>9</v>
@@ -2977,16 +4357,16 @@
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>9</v>
@@ -2994,16 +4374,16 @@
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>9</v>
@@ -3011,16 +4391,16 @@
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>195</v>
+        <v>258</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>9</v>
@@ -3028,16 +4408,16 @@
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>112</v>
+        <v>261</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>9</v>
@@ -3045,16 +4425,16 @@
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>9</v>
@@ -3062,16 +4442,16 @@
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>9</v>
@@ -3079,16 +4459,16 @@
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>9</v>
@@ -3096,16 +4476,16 @@
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>266</v>
+        <v>185</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>9</v>
@@ -3113,16 +4493,16 @@
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>9</v>
@@ -3130,16 +4510,16 @@
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>9</v>
@@ -3147,16 +4527,16 @@
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>9</v>
@@ -3164,16 +4544,16 @@
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>9</v>
@@ -3181,16 +4561,16 @@
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>9</v>
@@ -3198,16 +4578,16 @@
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>284</v>
+        <v>244</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>9</v>
@@ -3215,16 +4595,16 @@
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>9</v>
@@ -3232,16 +4612,16 @@
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>9</v>
@@ -3249,16 +4629,16 @@
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>9</v>
@@ -3266,16 +4646,16 @@
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>9</v>
@@ -3283,16 +4663,16 @@
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>9</v>
@@ -3300,16 +4680,16 @@
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>9</v>
@@ -3317,16 +4697,16 @@
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>9</v>
@@ -3334,16 +4714,16 @@
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>9</v>
@@ -3351,16 +4731,16 @@
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C108" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>9</v>
@@ -3368,16 +4748,16 @@
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>9</v>
@@ -3385,16 +4765,16 @@
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>9</v>
@@ -3402,16 +4782,16 @@
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>9</v>
@@ -3419,16 +4799,16 @@
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>24</v>
+        <v>325</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>9</v>
@@ -3436,16 +4816,16 @@
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>325</v>
+        <v>182</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>9</v>
@@ -3453,16 +4833,16 @@
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>9</v>
@@ -3470,16 +4850,16 @@
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C115" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>331</v>
+        <v>207</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>9</v>
@@ -3487,16 +4867,16 @@
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C116" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>334</v>
+        <v>130</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>9</v>
@@ -3564,7 +4944,7 @@
         <v>7</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>162</v>
+        <v>346</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>9</v>
@@ -3572,16 +4952,16 @@
     </row>
     <row r="121" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>9</v>
@@ -3589,16 +4969,16 @@
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>9</v>
@@ -3606,16 +4986,16 @@
     </row>
     <row r="123" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>284</v>
+        <v>355</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>9</v>
@@ -3623,16 +5003,16 @@
     </row>
     <row r="124" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>9</v>
@@ -3640,16 +5020,16 @@
     </row>
     <row r="125" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>358</v>
+        <v>213</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>9</v>
@@ -3657,18 +5037,2993 @@
     </row>
     <row r="126" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C126" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="E126" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C184" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C185" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="C186" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C187" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C188" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C189" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C190" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="C192" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C193" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C194" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C196" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="C197" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="C198" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="C199" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C200" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C201" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C202" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C203" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C204" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C205" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="C206" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C207" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C208" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C210" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="C212" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C213" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C220" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C221" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C222" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C228" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="C229" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="C231" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C234" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="C235" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C236" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="C237" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C238" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C241" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C242" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C243" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C244" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C245" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C246" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C247" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C248" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C249" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C250" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C253" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="258" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C259" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="262" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C262" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C263" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="264" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="265" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="266" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="268" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="269" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="271" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="273" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="274" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="275" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C276" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="277" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>754</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="278" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="279" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="280" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="282" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>768</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="283" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C283" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="284" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="285" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="286" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="287" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C287" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="288" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C288" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="289" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="290" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="291" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="292" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C292" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="293" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="294" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="295" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="296" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C296" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="297" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="298" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C298" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="299" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="300" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="301" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="E301" s="2" t="s">
         <v>9</v>
       </c>
     </row>
